--- a/xls/square_16_tri3_14_0.xlsx
+++ b/xls/square_16_tri3_14_0.xlsx
@@ -482,13 +482,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-1.7645551664757886</v>
+        <v>-2.3398823916786693</v>
       </c>
       <c r="J16">
-        <v>-2.094475638209769</v>
+        <v>-2.0958253936272064</v>
       </c>
       <c r="K16">
-        <v>-1.6294365429505588</v>
+        <v>-1.6119352095171091</v>
       </c>
     </row>
   </sheetData>
